--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:48:59+00:00</t>
+    <t>2026-04-25T16:59:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:59:12+00:00</t>
+    <t>2026-04-25T17:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:20:31+00:00</t>
+    <t>2026-04-25T17:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,19 +371,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:34:35+00:00</t>
+    <t>2026-04-25T21:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ATTCK2FHIR IG</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:04:27+00:00</t>
+    <t>2026-04-25T21:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:17:05+00:00</t>
+    <t>2026-04-25T21:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -371,7 +371,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:19:40+00:00</t>
+    <t>2026-04-25T21:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T18:07:37+00:00</t>
+    <t>2026-05-16T09:46:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-MITRE-ATTCK-Techniques.xlsx
+++ b/ValueSet-MITRE-ATTCK-Techniques.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.12</t>
+    <t>0.0.13</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T09:46:24+00:00</t>
+    <t>2026-05-16T09:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
